--- a/artfynd/A 25033-2023 artfynd.xlsx
+++ b/artfynd/A 25033-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25033-2023 artfynd.xlsx
+++ b/artfynd/A 25033-2023 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>120912490</v>
       </c>
       <c r="B4" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
